--- a/docs/resources/Mappings.xlsx
+++ b/docs/resources/Mappings.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Molgenis\repos\molgenis-emx2\docs\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AE2B27E-7A31-4A64-8120-CDB3372FA93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443A1FD4-5058-4A13-99AA-96AB49480615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="12000" xr2:uid="{F86F0FFA-F849-435E-8F15-A7532F91F404}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{F86F0FFA-F849-435E-8F15-A7532F91F404}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dataset mappings" sheetId="1" r:id="rId1"/>
+    <sheet name="Table mappings" sheetId="1" r:id="rId1"/>
     <sheet name="Variable mappings" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -48,15 +48,9 @@
     <t>order</t>
   </si>
   <si>
-    <t>target dataset</t>
-  </si>
-  <si>
     <t>target</t>
   </si>
   <si>
-    <t>source dataset</t>
-  </si>
-  <si>
     <t>source</t>
   </si>
   <si>
@@ -72,13 +66,19 @@
     <t>target variable</t>
   </si>
   <si>
-    <t>source variables other datasets.name</t>
-  </si>
-  <si>
-    <t>source variables other datasets.dataset</t>
-  </si>
-  <si>
     <t>source variables</t>
+  </si>
+  <si>
+    <t>source table</t>
+  </si>
+  <si>
+    <t>target table</t>
+  </si>
+  <si>
+    <t>source variables other tables.table</t>
+  </si>
+  <si>
+    <t>source variables other tables.name</t>
   </si>
 </sst>
 </file>
@@ -451,29 +451,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567CEEA9-5F71-49AF-BB90-1AD5AB1FBBB8}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.46484375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -493,53 +493,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F58A07B1-53BA-40D4-9576-224AC8829486}">
   <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -548,7 +548,7 @@
         <v>0</v>
       </c>
       <c r="M1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
